--- a/data/memories/memory_01/locales/es/documents/hr/Employee Registry v1.xlsx
+++ b/data/memories/memory_01/locales/es/documents/hr/Employee Registry v1.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Registry Version 1</t>
+          <t>Registro de Empleados Versión 1</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,55 +469,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Official Employee Registry</t>
+          <t>Registro Oficial de Empleados</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>This registry represents the approved employee records following the annual documentation review. It was prepared according to the employee management procedure.</t>
+          <t>Este registro representa los registros de empleados aprobados luego de la revisión anual de la documentación. Fue elaborado según el procedimiento de gestión de empleados.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Active Employees</t>
+          <t>Empleados activos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IDENTIFICACIÓN</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Empleado</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Fecha de inicio</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sarah K.</t>
+          <t>sara k.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laura L.</t>
+          <t>laura l.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -610,12 +610,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oliver M.</t>
+          <t>óliver m.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ÉL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M. R.</t>
+          <t>SEÑOR.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -679,77 +679,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Archived Review</t>
+          <t>Revisión archivada</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Registry Observations</t>
+          <t>Observaciones del Registro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The registry was compiled from previous employee records, department documentation and approved organisational information.</t>
+          <t>El registro se compiló a partir de registros anteriores de empleados, documentación del departamento e información organizacional aprobada.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>During validation, one historical reference could not be matched with current department structures. The record was retained pending further clarification.</t>
+          <t>Durante la validación, una referencia histórica no pudo coincidir con las estructuras departamentales actuales. El expediente se retuvo en espera de mayor aclaración.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Validation Checklist</t>
+          <t>Lista de verificación de validación</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>• Employee identifiers checked.</t>
+          <t>• Identificadores de empleados verificados.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>• Department assignments reviewed.</t>
+          <t>• Se revisan las tareas del departamento.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>• Employment status confirmed.</t>
+          <t>• Situación laboral confirmada.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>• Historical references compared.</t>
+          <t>• Referencias históricas comparadas.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Internal Comment</t>
+          <t>Comentario interno</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Future versions should preserve previous identifiers even when organisational changes affect department names.</t>
+          <t>Las versiones futuras deberían conservar los identificadores anteriores incluso cuando los cambios organizativos afecten a los nombres de los departamentos.</t>
         </is>
       </c>
     </row>
